--- a/capstone-project/public/templates/ModernFPShifters_Template.xlsx
+++ b/capstone-project/public/templates/ModernFPShifters_Template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Subdermal Implant</t>
   </si>
   <si>
-    <t>CCM/ Billings</t>
+    <t>CMM/ Billings</t>
   </si>
   <si>
     <t>BBT</t>
@@ -111,6 +111,21 @@
   <si>
     <t>GRAND TOTAL</t>
   </si>
+  <si>
+    <t>Prepared by:</t>
+  </si>
+  <si>
+    <t>Received by:</t>
+  </si>
+  <si>
+    <t>Name &amp; Signature</t>
+  </si>
+  <si>
+    <t>Approved by:</t>
+  </si>
+  <si>
+    <t>Name &amp; Signature of Provincial /City/Municipal Population Officer</t>
+  </si>
 </sst>
 </file>
 
@@ -119,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -204,6 +219,15 @@
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -231,7 +255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border/>
     <border>
       <left/>
@@ -328,11 +352,16 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -360,7 +389,7 @@
     <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -369,8 +398,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -378,21 +410,39 @@
     <xf borderId="9" fillId="3" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="3" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="4" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -676,7 +726,7 @@
     <col customWidth="1" min="6" max="6" width="14.63"/>
     <col customWidth="1" min="7" max="7" width="17.75"/>
     <col customWidth="1" min="8" max="8" width="19.5"/>
-    <col customWidth="1" min="9" max="9" width="12.0"/>
+    <col customWidth="1" min="9" max="9" width="15.88"/>
     <col customWidth="1" min="10" max="10" width="10.75"/>
     <col customWidth="1" min="11" max="11" width="10.88"/>
     <col customWidth="1" min="12" max="12" width="10.75"/>
@@ -886,7 +936,7 @@
       <c r="H12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="15" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -912,22 +962,22 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
@@ -938,22 +988,22 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="18"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
@@ -964,22 +1014,22 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="18"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
@@ -990,22 +1040,22 @@
       <c r="V15" s="12"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="18"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
@@ -1016,22 +1066,22 @@
       <c r="V16" s="12"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="18"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -1042,22 +1092,22 @@
       <c r="V17" s="12"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="18"/>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -1068,22 +1118,22 @@
       <c r="V18" s="12"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="18"/>
       <c r="O19" s="12"/>
       <c r="P19" s="12"/>
       <c r="Q19" s="12"/>
@@ -1094,22 +1144,22 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="18"/>
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
@@ -1120,22 +1170,22 @@
       <c r="V20" s="12"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="18"/>
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
@@ -1146,22 +1196,22 @@
       <c r="V21" s="12"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="18"/>
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -1172,22 +1222,22 @@
       <c r="V22" s="12"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="18"/>
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -1198,22 +1248,22 @@
       <c r="V23" s="12"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="18"/>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
@@ -1224,22 +1274,22 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" ht="26.25" customHeight="1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
@@ -1250,14 +1300,14 @@
       <c r="V25" s="12"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
@@ -1297,19 +1347,23 @@
       <c r="U27" s="12"/>
       <c r="V27" s="12"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" ht="21.75" customHeight="1">
       <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="B28" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
@@ -1323,17 +1377,16 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="26" t="s">
+        <v>35</v>
+      </c>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
@@ -1347,17 +1400,17 @@
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
@@ -1369,1432 +1422,1456 @@
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21"/>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
-      <c r="N42" s="21"/>
-      <c r="O42" s="21"/>
-      <c r="P42" s="21"/>
-      <c r="Q42" s="21"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="21"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21"/>
-      <c r="P44" s="21"/>
-      <c r="Q44" s="21"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="21"/>
-      <c r="O45" s="21"/>
-      <c r="P45" s="21"/>
-      <c r="Q45" s="21"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="21"/>
-      <c r="O46" s="21"/>
-      <c r="P46" s="21"/>
-      <c r="Q46" s="21"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="21"/>
-      <c r="P47" s="21"/>
-      <c r="Q47" s="21"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="21"/>
-      <c r="O48" s="21"/>
-      <c r="P48" s="21"/>
-      <c r="Q48" s="21"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
-      <c r="K49" s="21"/>
-      <c r="L49" s="21"/>
-      <c r="M49" s="21"/>
-      <c r="N49" s="21"/>
-      <c r="O49" s="21"/>
-      <c r="P49" s="21"/>
-      <c r="Q49" s="21"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="21"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="21"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="21"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
-      <c r="O52" s="21"/>
-      <c r="P52" s="21"/>
-      <c r="Q52" s="21"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
-      <c r="N53" s="21"/>
-      <c r="O53" s="21"/>
-      <c r="P53" s="21"/>
-      <c r="Q53" s="21"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="29"/>
+      <c r="Q53" s="29"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
-      <c r="O54" s="21"/>
-      <c r="P54" s="21"/>
-      <c r="Q54" s="21"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="21"/>
-      <c r="P55" s="21"/>
-      <c r="Q55" s="21"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="21"/>
-      <c r="N56" s="21"/>
-      <c r="O56" s="21"/>
-      <c r="P56" s="21"/>
-      <c r="Q56" s="21"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="21"/>
-      <c r="L57" s="21"/>
-      <c r="M57" s="21"/>
-      <c r="N57" s="21"/>
-      <c r="O57" s="21"/>
-      <c r="P57" s="21"/>
-      <c r="Q57" s="21"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="21"/>
-      <c r="P59" s="21"/>
-      <c r="Q59" s="21"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21"/>
-      <c r="Q60" s="21"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
-      <c r="L61" s="21"/>
-      <c r="M61" s="21"/>
-      <c r="N61" s="21"/>
-      <c r="O61" s="21"/>
-      <c r="P61" s="21"/>
-      <c r="Q61" s="21"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="21"/>
-      <c r="N62" s="21"/>
-      <c r="O62" s="21"/>
-      <c r="P62" s="21"/>
-      <c r="Q62" s="21"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
+      <c r="P62" s="29"/>
+      <c r="Q62" s="29"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="21"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="21"/>
-      <c r="O63" s="21"/>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="29"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
-      <c r="O64" s="21"/>
-      <c r="P64" s="21"/>
-      <c r="Q64" s="21"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="21"/>
-      <c r="O65" s="21"/>
-      <c r="P65" s="21"/>
-      <c r="Q65" s="21"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="29"/>
+      <c r="M65" s="29"/>
+      <c r="N65" s="29"/>
+      <c r="O65" s="29"/>
+      <c r="P65" s="29"/>
+      <c r="Q65" s="29"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="21"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="21"/>
-      <c r="M66" s="21"/>
-      <c r="N66" s="21"/>
-      <c r="O66" s="21"/>
-      <c r="P66" s="21"/>
-      <c r="Q66" s="21"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="29"/>
+      <c r="O66" s="29"/>
+      <c r="P66" s="29"/>
+      <c r="Q66" s="29"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="21"/>
-      <c r="M67" s="21"/>
-      <c r="N67" s="21"/>
-      <c r="O67" s="21"/>
-      <c r="P67" s="21"/>
-      <c r="Q67" s="21"/>
+      <c r="A67" s="29"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
+      <c r="A68" s="29"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+      <c r="P68" s="29"/>
+      <c r="Q68" s="29"/>
     </row>
     <row r="69" ht="16.5" customHeight="1">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
-      <c r="P69" s="21"/>
-      <c r="Q69" s="21"/>
+      <c r="A69" s="29"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
+      <c r="P69" s="29"/>
+      <c r="Q69" s="29"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="21"/>
-      <c r="Q70" s="21"/>
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="21"/>
-      <c r="Q71" s="21"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
+      <c r="L71" s="29"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="29"/>
+      <c r="P71" s="29"/>
+      <c r="Q71" s="29"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="29"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="29"/>
+      <c r="M72" s="29"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="29"/>
+      <c r="P72" s="29"/>
+      <c r="Q72" s="29"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="29"/>
+      <c r="J73" s="29"/>
+      <c r="K73" s="29"/>
+      <c r="L73" s="29"/>
+      <c r="M73" s="29"/>
+      <c r="N73" s="29"/>
+      <c r="O73" s="29"/>
+      <c r="P73" s="29"/>
+      <c r="Q73" s="29"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="29"/>
+      <c r="J74" s="29"/>
+      <c r="K74" s="29"/>
+      <c r="L74" s="29"/>
+      <c r="M74" s="29"/>
+      <c r="N74" s="29"/>
+      <c r="O74" s="29"/>
+      <c r="P74" s="29"/>
+      <c r="Q74" s="29"/>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29"/>
+      <c r="H75" s="29"/>
+      <c r="I75" s="29"/>
+      <c r="J75" s="29"/>
+      <c r="K75" s="29"/>
+      <c r="L75" s="29"/>
+      <c r="M75" s="29"/>
+      <c r="N75" s="29"/>
+      <c r="O75" s="29"/>
+      <c r="P75" s="29"/>
+      <c r="Q75" s="29"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29"/>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29"/>
+      <c r="O76" s="29"/>
+      <c r="P76" s="29"/>
+      <c r="Q76" s="29"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
+      <c r="A77" s="29"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="29"/>
+      <c r="L77" s="29"/>
+      <c r="M77" s="29"/>
+      <c r="N77" s="29"/>
+      <c r="O77" s="29"/>
+      <c r="P77" s="29"/>
+      <c r="Q77" s="29"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
+      <c r="A78" s="29"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="29"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="29"/>
+      <c r="K78" s="29"/>
+      <c r="L78" s="29"/>
+      <c r="M78" s="29"/>
+      <c r="N78" s="29"/>
+      <c r="O78" s="29"/>
+      <c r="P78" s="29"/>
+      <c r="Q78" s="29"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="21"/>
-      <c r="B79" s="21"/>
-      <c r="C79" s="21"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="21"/>
-      <c r="O79" s="21"/>
-      <c r="P79" s="21"/>
-      <c r="Q79" s="21"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
+      <c r="E79" s="29"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="29"/>
+      <c r="K79" s="29"/>
+      <c r="L79" s="29"/>
+      <c r="M79" s="29"/>
+      <c r="N79" s="29"/>
+      <c r="O79" s="29"/>
+      <c r="P79" s="29"/>
+      <c r="Q79" s="29"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="21"/>
-      <c r="B80" s="21"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
-      <c r="L80" s="21"/>
-      <c r="M80" s="21"/>
-      <c r="N80" s="21"/>
-      <c r="O80" s="21"/>
-      <c r="P80" s="21"/>
-      <c r="Q80" s="21"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
+      <c r="K80" s="29"/>
+      <c r="L80" s="29"/>
+      <c r="M80" s="29"/>
+      <c r="N80" s="29"/>
+      <c r="O80" s="29"/>
+      <c r="P80" s="29"/>
+      <c r="Q80" s="29"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="21"/>
-      <c r="B81" s="21"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="21"/>
-      <c r="N81" s="21"/>
-      <c r="O81" s="21"/>
-      <c r="P81" s="21"/>
-      <c r="Q81" s="21"/>
+      <c r="A81" s="29"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
+      <c r="E81" s="29"/>
+      <c r="F81" s="29"/>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="29"/>
+      <c r="L81" s="29"/>
+      <c r="M81" s="29"/>
+      <c r="N81" s="29"/>
+      <c r="O81" s="29"/>
+      <c r="P81" s="29"/>
+      <c r="Q81" s="29"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="21"/>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="21"/>
-      <c r="L82" s="21"/>
-      <c r="M82" s="21"/>
-      <c r="N82" s="21"/>
-      <c r="O82" s="21"/>
-      <c r="P82" s="21"/>
-      <c r="Q82" s="21"/>
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
+      <c r="L82" s="29"/>
+      <c r="M82" s="29"/>
+      <c r="N82" s="29"/>
+      <c r="O82" s="29"/>
+      <c r="P82" s="29"/>
+      <c r="Q82" s="29"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="21"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="21"/>
-      <c r="L83" s="21"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="21"/>
-      <c r="O83" s="21"/>
-      <c r="P83" s="21"/>
-      <c r="Q83" s="21"/>
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="29"/>
+      <c r="K83" s="29"/>
+      <c r="L83" s="29"/>
+      <c r="M83" s="29"/>
+      <c r="N83" s="29"/>
+      <c r="O83" s="29"/>
+      <c r="P83" s="29"/>
+      <c r="Q83" s="29"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="21"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
-      <c r="K84" s="21"/>
-      <c r="L84" s="21"/>
-      <c r="M84" s="21"/>
-      <c r="N84" s="21"/>
-      <c r="O84" s="21"/>
-      <c r="P84" s="21"/>
-      <c r="Q84" s="21"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="29"/>
+      <c r="K84" s="29"/>
+      <c r="L84" s="29"/>
+      <c r="M84" s="29"/>
+      <c r="N84" s="29"/>
+      <c r="O84" s="29"/>
+      <c r="P84" s="29"/>
+      <c r="Q84" s="29"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="21"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
-      <c r="K85" s="21"/>
-      <c r="L85" s="21"/>
-      <c r="M85" s="21"/>
-      <c r="N85" s="21"/>
-      <c r="O85" s="21"/>
-      <c r="P85" s="21"/>
-      <c r="Q85" s="21"/>
+      <c r="A85" s="29"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="29"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="29"/>
+      <c r="K85" s="29"/>
+      <c r="L85" s="29"/>
+      <c r="M85" s="29"/>
+      <c r="N85" s="29"/>
+      <c r="O85" s="29"/>
+      <c r="P85" s="29"/>
+      <c r="Q85" s="29"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="21"/>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21"/>
-      <c r="L86" s="21"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
-      <c r="P86" s="21"/>
-      <c r="Q86" s="21"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
+      <c r="E86" s="29"/>
+      <c r="F86" s="29"/>
+      <c r="G86" s="29"/>
+      <c r="H86" s="29"/>
+      <c r="I86" s="29"/>
+      <c r="J86" s="29"/>
+      <c r="K86" s="29"/>
+      <c r="L86" s="29"/>
+      <c r="M86" s="29"/>
+      <c r="N86" s="29"/>
+      <c r="O86" s="29"/>
+      <c r="P86" s="29"/>
+      <c r="Q86" s="29"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="21"/>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21"/>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
-      <c r="K87" s="21"/>
-      <c r="L87" s="21"/>
-      <c r="M87" s="21"/>
-      <c r="N87" s="21"/>
-      <c r="O87" s="21"/>
-      <c r="P87" s="21"/>
-      <c r="Q87" s="21"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
+      <c r="D87" s="29"/>
+      <c r="E87" s="29"/>
+      <c r="F87" s="29"/>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
+      <c r="I87" s="29"/>
+      <c r="J87" s="29"/>
+      <c r="K87" s="29"/>
+      <c r="L87" s="29"/>
+      <c r="M87" s="29"/>
+      <c r="N87" s="29"/>
+      <c r="O87" s="29"/>
+      <c r="P87" s="29"/>
+      <c r="Q87" s="29"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="21"/>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="21"/>
-      <c r="G88" s="21"/>
-      <c r="H88" s="21"/>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21"/>
-      <c r="K88" s="21"/>
-      <c r="L88" s="21"/>
-      <c r="M88" s="21"/>
-      <c r="N88" s="21"/>
-      <c r="O88" s="21"/>
-      <c r="P88" s="21"/>
-      <c r="Q88" s="21"/>
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+      <c r="D88" s="29"/>
+      <c r="E88" s="29"/>
+      <c r="F88" s="29"/>
+      <c r="G88" s="29"/>
+      <c r="H88" s="29"/>
+      <c r="I88" s="29"/>
+      <c r="J88" s="29"/>
+      <c r="K88" s="29"/>
+      <c r="L88" s="29"/>
+      <c r="M88" s="29"/>
+      <c r="N88" s="29"/>
+      <c r="O88" s="29"/>
+      <c r="P88" s="29"/>
+      <c r="Q88" s="29"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="21"/>
-      <c r="B89" s="21"/>
-      <c r="C89" s="21"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="21"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21"/>
-      <c r="I89" s="21"/>
-      <c r="J89" s="21"/>
-      <c r="K89" s="21"/>
-      <c r="L89" s="21"/>
-      <c r="M89" s="21"/>
-      <c r="N89" s="21"/>
-      <c r="O89" s="21"/>
-      <c r="P89" s="21"/>
-      <c r="Q89" s="21"/>
+      <c r="A89" s="29"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="29"/>
+      <c r="G89" s="29"/>
+      <c r="H89" s="29"/>
+      <c r="I89" s="29"/>
+      <c r="J89" s="29"/>
+      <c r="K89" s="29"/>
+      <c r="L89" s="29"/>
+      <c r="M89" s="29"/>
+      <c r="N89" s="29"/>
+      <c r="O89" s="29"/>
+      <c r="P89" s="29"/>
+      <c r="Q89" s="29"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="21"/>
-      <c r="B90" s="21"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
-      <c r="I90" s="21"/>
-      <c r="J90" s="21"/>
-      <c r="K90" s="21"/>
-      <c r="L90" s="21"/>
-      <c r="M90" s="21"/>
-      <c r="N90" s="21"/>
-      <c r="O90" s="21"/>
-      <c r="P90" s="21"/>
-      <c r="Q90" s="21"/>
+      <c r="A90" s="29"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
+      <c r="D90" s="29"/>
+      <c r="E90" s="29"/>
+      <c r="F90" s="29"/>
+      <c r="G90" s="29"/>
+      <c r="H90" s="29"/>
+      <c r="I90" s="29"/>
+      <c r="J90" s="29"/>
+      <c r="K90" s="29"/>
+      <c r="L90" s="29"/>
+      <c r="M90" s="29"/>
+      <c r="N90" s="29"/>
+      <c r="O90" s="29"/>
+      <c r="P90" s="29"/>
+      <c r="Q90" s="29"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="21"/>
-      <c r="B91" s="21"/>
-      <c r="C91" s="21"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21"/>
-      <c r="G91" s="21"/>
-      <c r="H91" s="21"/>
-      <c r="I91" s="21"/>
-      <c r="J91" s="21"/>
-      <c r="K91" s="21"/>
-      <c r="L91" s="21"/>
-      <c r="M91" s="21"/>
-      <c r="N91" s="21"/>
-      <c r="O91" s="21"/>
-      <c r="P91" s="21"/>
-      <c r="Q91" s="21"/>
+      <c r="A91" s="29"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="29"/>
+      <c r="E91" s="29"/>
+      <c r="F91" s="29"/>
+      <c r="G91" s="29"/>
+      <c r="H91" s="29"/>
+      <c r="I91" s="29"/>
+      <c r="J91" s="29"/>
+      <c r="K91" s="29"/>
+      <c r="L91" s="29"/>
+      <c r="M91" s="29"/>
+      <c r="N91" s="29"/>
+      <c r="O91" s="29"/>
+      <c r="P91" s="29"/>
+      <c r="Q91" s="29"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="21"/>
-      <c r="B92" s="21"/>
-      <c r="C92" s="21"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
-      <c r="J92" s="21"/>
-      <c r="K92" s="21"/>
-      <c r="L92" s="21"/>
-      <c r="M92" s="21"/>
-      <c r="N92" s="21"/>
-      <c r="O92" s="21"/>
-      <c r="P92" s="21"/>
-      <c r="Q92" s="21"/>
+      <c r="A92" s="29"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="29"/>
+      <c r="E92" s="29"/>
+      <c r="F92" s="29"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="29"/>
+      <c r="I92" s="29"/>
+      <c r="J92" s="29"/>
+      <c r="K92" s="29"/>
+      <c r="L92" s="29"/>
+      <c r="M92" s="29"/>
+      <c r="N92" s="29"/>
+      <c r="O92" s="29"/>
+      <c r="P92" s="29"/>
+      <c r="Q92" s="29"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="21"/>
-      <c r="B93" s="21"/>
-      <c r="C93" s="21"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
-      <c r="I93" s="21"/>
-      <c r="J93" s="21"/>
-      <c r="K93" s="21"/>
-      <c r="L93" s="21"/>
-      <c r="M93" s="21"/>
-      <c r="N93" s="21"/>
-      <c r="O93" s="21"/>
-      <c r="P93" s="21"/>
-      <c r="Q93" s="21"/>
+      <c r="A93" s="29"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="29"/>
+      <c r="E93" s="29"/>
+      <c r="F93" s="29"/>
+      <c r="G93" s="29"/>
+      <c r="H93" s="29"/>
+      <c r="I93" s="29"/>
+      <c r="J93" s="29"/>
+      <c r="K93" s="29"/>
+      <c r="L93" s="29"/>
+      <c r="M93" s="29"/>
+      <c r="N93" s="29"/>
+      <c r="O93" s="29"/>
+      <c r="P93" s="29"/>
+      <c r="Q93" s="29"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="21"/>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21"/>
-      <c r="K94" s="21"/>
-      <c r="L94" s="21"/>
-      <c r="M94" s="21"/>
-      <c r="N94" s="21"/>
-      <c r="O94" s="21"/>
-      <c r="P94" s="21"/>
-      <c r="Q94" s="21"/>
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
+      <c r="E94" s="29"/>
+      <c r="F94" s="29"/>
+      <c r="G94" s="29"/>
+      <c r="H94" s="29"/>
+      <c r="I94" s="29"/>
+      <c r="J94" s="29"/>
+      <c r="K94" s="29"/>
+      <c r="L94" s="29"/>
+      <c r="M94" s="29"/>
+      <c r="N94" s="29"/>
+      <c r="O94" s="29"/>
+      <c r="P94" s="29"/>
+      <c r="Q94" s="29"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="21"/>
-      <c r="B95" s="21"/>
-      <c r="C95" s="21"/>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="21"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21"/>
-      <c r="I95" s="21"/>
-      <c r="J95" s="21"/>
-      <c r="K95" s="21"/>
-      <c r="L95" s="21"/>
-      <c r="M95" s="21"/>
-      <c r="N95" s="21"/>
-      <c r="O95" s="21"/>
-      <c r="P95" s="21"/>
-      <c r="Q95" s="21"/>
+      <c r="A95" s="29"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
+      <c r="E95" s="29"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="29"/>
+      <c r="H95" s="29"/>
+      <c r="I95" s="29"/>
+      <c r="J95" s="29"/>
+      <c r="K95" s="29"/>
+      <c r="L95" s="29"/>
+      <c r="M95" s="29"/>
+      <c r="N95" s="29"/>
+      <c r="O95" s="29"/>
+      <c r="P95" s="29"/>
+      <c r="Q95" s="29"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="21"/>
-      <c r="B96" s="21"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
-      <c r="I96" s="21"/>
-      <c r="J96" s="21"/>
-      <c r="K96" s="21"/>
-      <c r="L96" s="21"/>
-      <c r="M96" s="21"/>
-      <c r="N96" s="21"/>
-      <c r="O96" s="21"/>
-      <c r="P96" s="21"/>
-      <c r="Q96" s="21"/>
+      <c r="A96" s="29"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="29"/>
+      <c r="E96" s="29"/>
+      <c r="F96" s="29"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+      <c r="I96" s="29"/>
+      <c r="J96" s="29"/>
+      <c r="K96" s="29"/>
+      <c r="L96" s="29"/>
+      <c r="M96" s="29"/>
+      <c r="N96" s="29"/>
+      <c r="O96" s="29"/>
+      <c r="P96" s="29"/>
+      <c r="Q96" s="29"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="21"/>
-      <c r="B97" s="21"/>
-      <c r="C97" s="21"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21"/>
-      <c r="K97" s="21"/>
-      <c r="L97" s="21"/>
-      <c r="M97" s="21"/>
-      <c r="N97" s="21"/>
-      <c r="O97" s="21"/>
-      <c r="P97" s="21"/>
-      <c r="Q97" s="21"/>
+      <c r="A97" s="29"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="29"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="29"/>
+      <c r="J97" s="29"/>
+      <c r="K97" s="29"/>
+      <c r="L97" s="29"/>
+      <c r="M97" s="29"/>
+      <c r="N97" s="29"/>
+      <c r="O97" s="29"/>
+      <c r="P97" s="29"/>
+      <c r="Q97" s="29"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="21"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="21"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="21"/>
-      <c r="J98" s="21"/>
-      <c r="K98" s="21"/>
-      <c r="L98" s="21"/>
-      <c r="M98" s="21"/>
-      <c r="N98" s="21"/>
-      <c r="O98" s="21"/>
-      <c r="P98" s="21"/>
-      <c r="Q98" s="21"/>
+      <c r="A98" s="29"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="29"/>
+      <c r="J98" s="29"/>
+      <c r="K98" s="29"/>
+      <c r="L98" s="29"/>
+      <c r="M98" s="29"/>
+      <c r="N98" s="29"/>
+      <c r="O98" s="29"/>
+      <c r="P98" s="29"/>
+      <c r="Q98" s="29"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="21"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="21"/>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="21"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="21"/>
-      <c r="J99" s="21"/>
-      <c r="K99" s="21"/>
-      <c r="L99" s="21"/>
-      <c r="M99" s="21"/>
-      <c r="N99" s="21"/>
-      <c r="O99" s="21"/>
-      <c r="P99" s="21"/>
-      <c r="Q99" s="21"/>
+      <c r="A99" s="29"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="29"/>
+      <c r="E99" s="29"/>
+      <c r="F99" s="29"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+      <c r="I99" s="29"/>
+      <c r="J99" s="29"/>
+      <c r="K99" s="29"/>
+      <c r="L99" s="29"/>
+      <c r="M99" s="29"/>
+      <c r="N99" s="29"/>
+      <c r="O99" s="29"/>
+      <c r="P99" s="29"/>
+      <c r="Q99" s="29"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="21"/>
-      <c r="B100" s="21"/>
-      <c r="C100" s="21"/>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-      <c r="J100" s="21"/>
-      <c r="K100" s="21"/>
-      <c r="L100" s="21"/>
-      <c r="M100" s="21"/>
-      <c r="N100" s="21"/>
-      <c r="O100" s="21"/>
-      <c r="P100" s="21"/>
-      <c r="Q100" s="21"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="29"/>
+      <c r="E100" s="29"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+      <c r="I100" s="29"/>
+      <c r="J100" s="29"/>
+      <c r="K100" s="29"/>
+      <c r="L100" s="29"/>
+      <c r="M100" s="29"/>
+      <c r="N100" s="29"/>
+      <c r="O100" s="29"/>
+      <c r="P100" s="29"/>
+      <c r="Q100" s="29"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="21"/>
-      <c r="B101" s="21"/>
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
-      <c r="K101" s="21"/>
-      <c r="L101" s="21"/>
-      <c r="M101" s="21"/>
-      <c r="N101" s="21"/>
-      <c r="O101" s="21"/>
-      <c r="P101" s="21"/>
-      <c r="Q101" s="21"/>
+      <c r="A101" s="29"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="29"/>
+      <c r="E101" s="29"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="29"/>
+      <c r="H101" s="29"/>
+      <c r="I101" s="29"/>
+      <c r="J101" s="29"/>
+      <c r="K101" s="29"/>
+      <c r="L101" s="29"/>
+      <c r="M101" s="29"/>
+      <c r="N101" s="29"/>
+      <c r="O101" s="29"/>
+      <c r="P101" s="29"/>
+      <c r="Q101" s="29"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="21"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21"/>
-      <c r="K102" s="21"/>
-      <c r="L102" s="21"/>
-      <c r="M102" s="21"/>
-      <c r="N102" s="21"/>
-      <c r="O102" s="21"/>
-      <c r="P102" s="21"/>
-      <c r="Q102" s="21"/>
+      <c r="A102" s="29"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="29"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="29"/>
+      <c r="H102" s="29"/>
+      <c r="I102" s="29"/>
+      <c r="J102" s="29"/>
+      <c r="K102" s="29"/>
+      <c r="L102" s="29"/>
+      <c r="M102" s="29"/>
+      <c r="N102" s="29"/>
+      <c r="O102" s="29"/>
+      <c r="P102" s="29"/>
+      <c r="Q102" s="29"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="21"/>
-      <c r="B103" s="21"/>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21"/>
-      <c r="K103" s="21"/>
-      <c r="L103" s="21"/>
-      <c r="M103" s="21"/>
-      <c r="N103" s="21"/>
-      <c r="O103" s="21"/>
-      <c r="P103" s="21"/>
-      <c r="Q103" s="21"/>
+      <c r="A103" s="29"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="29"/>
+      <c r="E103" s="29"/>
+      <c r="F103" s="29"/>
+      <c r="G103" s="29"/>
+      <c r="H103" s="29"/>
+      <c r="I103" s="29"/>
+      <c r="J103" s="29"/>
+      <c r="K103" s="29"/>
+      <c r="L103" s="29"/>
+      <c r="M103" s="29"/>
+      <c r="N103" s="29"/>
+      <c r="O103" s="29"/>
+      <c r="P103" s="29"/>
+      <c r="Q103" s="29"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="21"/>
-      <c r="B104" s="21"/>
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-      <c r="I104" s="21"/>
-      <c r="J104" s="21"/>
-      <c r="K104" s="21"/>
-      <c r="L104" s="21"/>
-      <c r="M104" s="21"/>
-      <c r="N104" s="21"/>
-      <c r="O104" s="21"/>
-      <c r="P104" s="21"/>
-      <c r="Q104" s="21"/>
+      <c r="A104" s="29"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
+      <c r="D104" s="29"/>
+      <c r="E104" s="29"/>
+      <c r="F104" s="29"/>
+      <c r="G104" s="29"/>
+      <c r="H104" s="29"/>
+      <c r="I104" s="29"/>
+      <c r="J104" s="29"/>
+      <c r="K104" s="29"/>
+      <c r="L104" s="29"/>
+      <c r="M104" s="29"/>
+      <c r="N104" s="29"/>
+      <c r="O104" s="29"/>
+      <c r="P104" s="29"/>
+      <c r="Q104" s="29"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="21"/>
-      <c r="B105" s="21"/>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="21"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
-      <c r="I105" s="21"/>
-      <c r="J105" s="21"/>
-      <c r="K105" s="21"/>
-      <c r="L105" s="21"/>
-      <c r="M105" s="21"/>
-      <c r="N105" s="21"/>
-      <c r="O105" s="21"/>
-      <c r="P105" s="21"/>
-      <c r="Q105" s="21"/>
+      <c r="A105" s="29"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="29"/>
+      <c r="E105" s="29"/>
+      <c r="F105" s="29"/>
+      <c r="G105" s="29"/>
+      <c r="H105" s="29"/>
+      <c r="I105" s="29"/>
+      <c r="J105" s="29"/>
+      <c r="K105" s="29"/>
+      <c r="L105" s="29"/>
+      <c r="M105" s="29"/>
+      <c r="N105" s="29"/>
+      <c r="O105" s="29"/>
+      <c r="P105" s="29"/>
+      <c r="Q105" s="29"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="21"/>
-      <c r="B106" s="21"/>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="21"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="21"/>
-      <c r="I106" s="21"/>
-      <c r="J106" s="21"/>
-      <c r="K106" s="21"/>
-      <c r="L106" s="21"/>
-      <c r="M106" s="21"/>
-      <c r="N106" s="21"/>
-      <c r="O106" s="21"/>
-      <c r="P106" s="21"/>
-      <c r="Q106" s="21"/>
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+      <c r="D106" s="29"/>
+      <c r="E106" s="29"/>
+      <c r="F106" s="29"/>
+      <c r="G106" s="29"/>
+      <c r="H106" s="29"/>
+      <c r="I106" s="29"/>
+      <c r="J106" s="29"/>
+      <c r="K106" s="29"/>
+      <c r="L106" s="29"/>
+      <c r="M106" s="29"/>
+      <c r="N106" s="29"/>
+      <c r="O106" s="29"/>
+      <c r="P106" s="29"/>
+      <c r="Q106" s="29"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="21"/>
-      <c r="B107" s="21"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="21"/>
-      <c r="L107" s="21"/>
-      <c r="M107" s="21"/>
-      <c r="N107" s="21"/>
-      <c r="O107" s="21"/>
-      <c r="P107" s="21"/>
-      <c r="Q107" s="21"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="29"/>
+      <c r="E107" s="29"/>
+      <c r="F107" s="29"/>
+      <c r="G107" s="29"/>
+      <c r="H107" s="29"/>
+      <c r="I107" s="29"/>
+      <c r="J107" s="29"/>
+      <c r="K107" s="29"/>
+      <c r="L107" s="29"/>
+      <c r="M107" s="29"/>
+      <c r="N107" s="29"/>
+      <c r="O107" s="29"/>
+      <c r="P107" s="29"/>
+      <c r="Q107" s="29"/>
     </row>
     <row r="108" ht="14.25" customHeight="1"/>
     <row r="109" ht="14.25" customHeight="1"/>
@@ -3690,15 +3767,21 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="E34:I34"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="B11:M11"/>
     <mergeCell ref="N11:N12"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/capstone-project/public/templates/ModernFPShifters_Template.xlsx
+++ b/capstone-project/public/templates/ModernFPShifters_Template.xlsx
@@ -115,7 +115,7 @@
     <t>Prepared by:</t>
   </si>
   <si>
-    <t>Received by:</t>
+    <t>Reviewed by:</t>
   </si>
   <si>
     <t>Name &amp; Signature</t>
@@ -361,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -431,6 +431,9 @@
     <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -1357,7 +1360,7 @@
       <c r="E28" s="24"/>
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I28" s="23"/>
@@ -1378,13 +1381,13 @@
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="12"/>
       <c r="B29" s="25"/>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="27" t="s">
         <v>35</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="27" t="s">
         <v>35</v>
       </c>
       <c r="M29" s="12"/>
@@ -1423,35 +1426,35 @@
       <c r="V30" s="12"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="22" t="s">
         <v>36</v>
       </c>
@@ -1460,1418 +1463,1418 @@
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="29"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="25"/>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="29"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="29"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="29"/>
-      <c r="O53" s="29"/>
-      <c r="P53" s="29"/>
-      <c r="Q53" s="29"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
-      <c r="Q54" s="29"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
-      <c r="Q56" s="29"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30"/>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
-      <c r="K59" s="29"/>
-      <c r="L59" s="29"/>
-      <c r="M59" s="29"/>
-      <c r="N59" s="29"/>
-      <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
-      <c r="Q59" s="29"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="29"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="29"/>
-      <c r="K62" s="29"/>
-      <c r="L62" s="29"/>
-      <c r="M62" s="29"/>
-      <c r="N62" s="29"/>
-      <c r="O62" s="29"/>
-      <c r="P62" s="29"/>
-      <c r="Q62" s="29"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="30"/>
+      <c r="O62" s="30"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="30"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="30"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="29"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="29"/>
-      <c r="K65" s="29"/>
-      <c r="L65" s="29"/>
-      <c r="M65" s="29"/>
-      <c r="N65" s="29"/>
-      <c r="O65" s="29"/>
-      <c r="P65" s="29"/>
-      <c r="Q65" s="29"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="30"/>
+      <c r="N65" s="30"/>
+      <c r="O65" s="30"/>
+      <c r="P65" s="30"/>
+      <c r="Q65" s="30"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
-      <c r="O66" s="29"/>
-      <c r="P66" s="29"/>
-      <c r="Q66" s="29"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="30"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="29"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="29"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="29"/>
-      <c r="Q68" s="29"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="30"/>
     </row>
     <row r="69" ht="16.5" customHeight="1">
-      <c r="A69" s="29"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29"/>
-      <c r="P69" s="29"/>
-      <c r="Q69" s="29"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="29"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="29"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
-      <c r="O71" s="29"/>
-      <c r="P71" s="29"/>
-      <c r="Q71" s="29"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
+      <c r="N71" s="30"/>
+      <c r="O71" s="30"/>
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="29"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="29"/>
-      <c r="M72" s="29"/>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
-      <c r="Q72" s="29"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
+      <c r="M72" s="30"/>
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="29"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="29"/>
-      <c r="L73" s="29"/>
-      <c r="M73" s="29"/>
-      <c r="N73" s="29"/>
-      <c r="O73" s="29"/>
-      <c r="P73" s="29"/>
-      <c r="Q73" s="29"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
+      <c r="M73" s="30"/>
+      <c r="N73" s="30"/>
+      <c r="O73" s="30"/>
+      <c r="P73" s="30"/>
+      <c r="Q73" s="30"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="29"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="29"/>
-      <c r="L74" s="29"/>
-      <c r="M74" s="29"/>
-      <c r="N74" s="29"/>
-      <c r="O74" s="29"/>
-      <c r="P74" s="29"/>
-      <c r="Q74" s="29"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
+      <c r="M74" s="30"/>
+      <c r="N74" s="30"/>
+      <c r="O74" s="30"/>
+      <c r="P74" s="30"/>
+      <c r="Q74" s="30"/>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="29"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-      <c r="J75" s="29"/>
-      <c r="K75" s="29"/>
-      <c r="L75" s="29"/>
-      <c r="M75" s="29"/>
-      <c r="N75" s="29"/>
-      <c r="O75" s="29"/>
-      <c r="P75" s="29"/>
-      <c r="Q75" s="29"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="30"/>
+      <c r="M75" s="30"/>
+      <c r="N75" s="30"/>
+      <c r="O75" s="30"/>
+      <c r="P75" s="30"/>
+      <c r="Q75" s="30"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="29"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
-      <c r="L76" s="29"/>
-      <c r="M76" s="29"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="29"/>
-      <c r="P76" s="29"/>
-      <c r="Q76" s="29"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="30"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="29"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
-      <c r="L77" s="29"/>
-      <c r="M77" s="29"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="29"/>
-      <c r="P77" s="29"/>
-      <c r="Q77" s="29"/>
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="30"/>
+      <c r="M77" s="30"/>
+      <c r="N77" s="30"/>
+      <c r="O77" s="30"/>
+      <c r="P77" s="30"/>
+      <c r="Q77" s="30"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="29"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="29"/>
-      <c r="K78" s="29"/>
-      <c r="L78" s="29"/>
-      <c r="M78" s="29"/>
-      <c r="N78" s="29"/>
-      <c r="O78" s="29"/>
-      <c r="P78" s="29"/>
-      <c r="Q78" s="29"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
+      <c r="L78" s="30"/>
+      <c r="M78" s="30"/>
+      <c r="N78" s="30"/>
+      <c r="O78" s="30"/>
+      <c r="P78" s="30"/>
+      <c r="Q78" s="30"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="29"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="29"/>
-      <c r="L79" s="29"/>
-      <c r="M79" s="29"/>
-      <c r="N79" s="29"/>
-      <c r="O79" s="29"/>
-      <c r="P79" s="29"/>
-      <c r="Q79" s="29"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="30"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="29"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="29"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
-      <c r="J80" s="29"/>
-      <c r="K80" s="29"/>
-      <c r="L80" s="29"/>
-      <c r="M80" s="29"/>
-      <c r="N80" s="29"/>
-      <c r="O80" s="29"/>
-      <c r="P80" s="29"/>
-      <c r="Q80" s="29"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="30"/>
+      <c r="M80" s="30"/>
+      <c r="N80" s="30"/>
+      <c r="O80" s="30"/>
+      <c r="P80" s="30"/>
+      <c r="Q80" s="30"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="29"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="29"/>
-      <c r="K81" s="29"/>
-      <c r="L81" s="29"/>
-      <c r="M81" s="29"/>
-      <c r="N81" s="29"/>
-      <c r="O81" s="29"/>
-      <c r="P81" s="29"/>
-      <c r="Q81" s="29"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
+      <c r="M81" s="30"/>
+      <c r="N81" s="30"/>
+      <c r="O81" s="30"/>
+      <c r="P81" s="30"/>
+      <c r="Q81" s="30"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="29"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
-      <c r="L82" s="29"/>
-      <c r="M82" s="29"/>
-      <c r="N82" s="29"/>
-      <c r="O82" s="29"/>
-      <c r="P82" s="29"/>
-      <c r="Q82" s="29"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="30"/>
+      <c r="M82" s="30"/>
+      <c r="N82" s="30"/>
+      <c r="O82" s="30"/>
+      <c r="P82" s="30"/>
+      <c r="Q82" s="30"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="29"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="29"/>
-      <c r="K83" s="29"/>
-      <c r="L83" s="29"/>
-      <c r="M83" s="29"/>
-      <c r="N83" s="29"/>
-      <c r="O83" s="29"/>
-      <c r="P83" s="29"/>
-      <c r="Q83" s="29"/>
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
+      <c r="N83" s="30"/>
+      <c r="O83" s="30"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="30"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="29"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
-      <c r="H84" s="29"/>
-      <c r="I84" s="29"/>
-      <c r="J84" s="29"/>
-      <c r="K84" s="29"/>
-      <c r="L84" s="29"/>
-      <c r="M84" s="29"/>
-      <c r="N84" s="29"/>
-      <c r="O84" s="29"/>
-      <c r="P84" s="29"/>
-      <c r="Q84" s="29"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="30"/>
+      <c r="L84" s="30"/>
+      <c r="M84" s="30"/>
+      <c r="N84" s="30"/>
+      <c r="O84" s="30"/>
+      <c r="P84" s="30"/>
+      <c r="Q84" s="30"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="29"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="29"/>
-      <c r="J85" s="29"/>
-      <c r="K85" s="29"/>
-      <c r="L85" s="29"/>
-      <c r="M85" s="29"/>
-      <c r="N85" s="29"/>
-      <c r="O85" s="29"/>
-      <c r="P85" s="29"/>
-      <c r="Q85" s="29"/>
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="30"/>
+      <c r="M85" s="30"/>
+      <c r="N85" s="30"/>
+      <c r="O85" s="30"/>
+      <c r="P85" s="30"/>
+      <c r="Q85" s="30"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="29"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="29"/>
-      <c r="E86" s="29"/>
-      <c r="F86" s="29"/>
-      <c r="G86" s="29"/>
-      <c r="H86" s="29"/>
-      <c r="I86" s="29"/>
-      <c r="J86" s="29"/>
-      <c r="K86" s="29"/>
-      <c r="L86" s="29"/>
-      <c r="M86" s="29"/>
-      <c r="N86" s="29"/>
-      <c r="O86" s="29"/>
-      <c r="P86" s="29"/>
-      <c r="Q86" s="29"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
+      <c r="M86" s="30"/>
+      <c r="N86" s="30"/>
+      <c r="O86" s="30"/>
+      <c r="P86" s="30"/>
+      <c r="Q86" s="30"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="29"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
-      <c r="E87" s="29"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29"/>
-      <c r="H87" s="29"/>
-      <c r="I87" s="29"/>
-      <c r="J87" s="29"/>
-      <c r="K87" s="29"/>
-      <c r="L87" s="29"/>
-      <c r="M87" s="29"/>
-      <c r="N87" s="29"/>
-      <c r="O87" s="29"/>
-      <c r="P87" s="29"/>
-      <c r="Q87" s="29"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="30"/>
+      <c r="K87" s="30"/>
+      <c r="L87" s="30"/>
+      <c r="M87" s="30"/>
+      <c r="N87" s="30"/>
+      <c r="O87" s="30"/>
+      <c r="P87" s="30"/>
+      <c r="Q87" s="30"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="29"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="29"/>
-      <c r="E88" s="29"/>
-      <c r="F88" s="29"/>
-      <c r="G88" s="29"/>
-      <c r="H88" s="29"/>
-      <c r="I88" s="29"/>
-      <c r="J88" s="29"/>
-      <c r="K88" s="29"/>
-      <c r="L88" s="29"/>
-      <c r="M88" s="29"/>
-      <c r="N88" s="29"/>
-      <c r="O88" s="29"/>
-      <c r="P88" s="29"/>
-      <c r="Q88" s="29"/>
+      <c r="A88" s="30"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
+      <c r="H88" s="30"/>
+      <c r="I88" s="30"/>
+      <c r="J88" s="30"/>
+      <c r="K88" s="30"/>
+      <c r="L88" s="30"/>
+      <c r="M88" s="30"/>
+      <c r="N88" s="30"/>
+      <c r="O88" s="30"/>
+      <c r="P88" s="30"/>
+      <c r="Q88" s="30"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="29"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="29"/>
-      <c r="E89" s="29"/>
-      <c r="F89" s="29"/>
-      <c r="G89" s="29"/>
-      <c r="H89" s="29"/>
-      <c r="I89" s="29"/>
-      <c r="J89" s="29"/>
-      <c r="K89" s="29"/>
-      <c r="L89" s="29"/>
-      <c r="M89" s="29"/>
-      <c r="N89" s="29"/>
-      <c r="O89" s="29"/>
-      <c r="P89" s="29"/>
-      <c r="Q89" s="29"/>
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="30"/>
+      <c r="H89" s="30"/>
+      <c r="I89" s="30"/>
+      <c r="J89" s="30"/>
+      <c r="K89" s="30"/>
+      <c r="L89" s="30"/>
+      <c r="M89" s="30"/>
+      <c r="N89" s="30"/>
+      <c r="O89" s="30"/>
+      <c r="P89" s="30"/>
+      <c r="Q89" s="30"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="29"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
-      <c r="F90" s="29"/>
-      <c r="G90" s="29"/>
-      <c r="H90" s="29"/>
-      <c r="I90" s="29"/>
-      <c r="J90" s="29"/>
-      <c r="K90" s="29"/>
-      <c r="L90" s="29"/>
-      <c r="M90" s="29"/>
-      <c r="N90" s="29"/>
-      <c r="O90" s="29"/>
-      <c r="P90" s="29"/>
-      <c r="Q90" s="29"/>
+      <c r="A90" s="30"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
+      <c r="K90" s="30"/>
+      <c r="L90" s="30"/>
+      <c r="M90" s="30"/>
+      <c r="N90" s="30"/>
+      <c r="O90" s="30"/>
+      <c r="P90" s="30"/>
+      <c r="Q90" s="30"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="29"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29"/>
-      <c r="H91" s="29"/>
-      <c r="I91" s="29"/>
-      <c r="J91" s="29"/>
-      <c r="K91" s="29"/>
-      <c r="L91" s="29"/>
-      <c r="M91" s="29"/>
-      <c r="N91" s="29"/>
-      <c r="O91" s="29"/>
-      <c r="P91" s="29"/>
-      <c r="Q91" s="29"/>
+      <c r="A91" s="30"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
+      <c r="H91" s="30"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="30"/>
+      <c r="K91" s="30"/>
+      <c r="L91" s="30"/>
+      <c r="M91" s="30"/>
+      <c r="N91" s="30"/>
+      <c r="O91" s="30"/>
+      <c r="P91" s="30"/>
+      <c r="Q91" s="30"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="29"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
-      <c r="F92" s="29"/>
-      <c r="G92" s="29"/>
-      <c r="H92" s="29"/>
-      <c r="I92" s="29"/>
-      <c r="J92" s="29"/>
-      <c r="K92" s="29"/>
-      <c r="L92" s="29"/>
-      <c r="M92" s="29"/>
-      <c r="N92" s="29"/>
-      <c r="O92" s="29"/>
-      <c r="P92" s="29"/>
-      <c r="Q92" s="29"/>
+      <c r="A92" s="30"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="30"/>
+      <c r="K92" s="30"/>
+      <c r="L92" s="30"/>
+      <c r="M92" s="30"/>
+      <c r="N92" s="30"/>
+      <c r="O92" s="30"/>
+      <c r="P92" s="30"/>
+      <c r="Q92" s="30"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="29"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="29"/>
-      <c r="I93" s="29"/>
-      <c r="J93" s="29"/>
-      <c r="K93" s="29"/>
-      <c r="L93" s="29"/>
-      <c r="M93" s="29"/>
-      <c r="N93" s="29"/>
-      <c r="O93" s="29"/>
-      <c r="P93" s="29"/>
-      <c r="Q93" s="29"/>
+      <c r="A93" s="30"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
+      <c r="H93" s="30"/>
+      <c r="I93" s="30"/>
+      <c r="J93" s="30"/>
+      <c r="K93" s="30"/>
+      <c r="L93" s="30"/>
+      <c r="M93" s="30"/>
+      <c r="N93" s="30"/>
+      <c r="O93" s="30"/>
+      <c r="P93" s="30"/>
+      <c r="Q93" s="30"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="29"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
-      <c r="G94" s="29"/>
-      <c r="H94" s="29"/>
-      <c r="I94" s="29"/>
-      <c r="J94" s="29"/>
-      <c r="K94" s="29"/>
-      <c r="L94" s="29"/>
-      <c r="M94" s="29"/>
-      <c r="N94" s="29"/>
-      <c r="O94" s="29"/>
-      <c r="P94" s="29"/>
-      <c r="Q94" s="29"/>
+      <c r="A94" s="30"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="30"/>
+      <c r="I94" s="30"/>
+      <c r="J94" s="30"/>
+      <c r="K94" s="30"/>
+      <c r="L94" s="30"/>
+      <c r="M94" s="30"/>
+      <c r="N94" s="30"/>
+      <c r="O94" s="30"/>
+      <c r="P94" s="30"/>
+      <c r="Q94" s="30"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="29"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="29"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="29"/>
-      <c r="H95" s="29"/>
-      <c r="I95" s="29"/>
-      <c r="J95" s="29"/>
-      <c r="K95" s="29"/>
-      <c r="L95" s="29"/>
-      <c r="M95" s="29"/>
-      <c r="N95" s="29"/>
-      <c r="O95" s="29"/>
-      <c r="P95" s="29"/>
-      <c r="Q95" s="29"/>
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+      <c r="J95" s="30"/>
+      <c r="K95" s="30"/>
+      <c r="L95" s="30"/>
+      <c r="M95" s="30"/>
+      <c r="N95" s="30"/>
+      <c r="O95" s="30"/>
+      <c r="P95" s="30"/>
+      <c r="Q95" s="30"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="29"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="29"/>
-      <c r="E96" s="29"/>
-      <c r="F96" s="29"/>
-      <c r="G96" s="29"/>
-      <c r="H96" s="29"/>
-      <c r="I96" s="29"/>
-      <c r="J96" s="29"/>
-      <c r="K96" s="29"/>
-      <c r="L96" s="29"/>
-      <c r="M96" s="29"/>
-      <c r="N96" s="29"/>
-      <c r="O96" s="29"/>
-      <c r="P96" s="29"/>
-      <c r="Q96" s="29"/>
+      <c r="A96" s="30"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+      <c r="J96" s="30"/>
+      <c r="K96" s="30"/>
+      <c r="L96" s="30"/>
+      <c r="M96" s="30"/>
+      <c r="N96" s="30"/>
+      <c r="O96" s="30"/>
+      <c r="P96" s="30"/>
+      <c r="Q96" s="30"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="29"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="29"/>
-      <c r="H97" s="29"/>
-      <c r="I97" s="29"/>
-      <c r="J97" s="29"/>
-      <c r="K97" s="29"/>
-      <c r="L97" s="29"/>
-      <c r="M97" s="29"/>
-      <c r="N97" s="29"/>
-      <c r="O97" s="29"/>
-      <c r="P97" s="29"/>
-      <c r="Q97" s="29"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
+      <c r="I97" s="30"/>
+      <c r="J97" s="30"/>
+      <c r="K97" s="30"/>
+      <c r="L97" s="30"/>
+      <c r="M97" s="30"/>
+      <c r="N97" s="30"/>
+      <c r="O97" s="30"/>
+      <c r="P97" s="30"/>
+      <c r="Q97" s="30"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="29"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
-      <c r="G98" s="29"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="29"/>
-      <c r="J98" s="29"/>
-      <c r="K98" s="29"/>
-      <c r="L98" s="29"/>
-      <c r="M98" s="29"/>
-      <c r="N98" s="29"/>
-      <c r="O98" s="29"/>
-      <c r="P98" s="29"/>
-      <c r="Q98" s="29"/>
+      <c r="A98" s="30"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+      <c r="J98" s="30"/>
+      <c r="K98" s="30"/>
+      <c r="L98" s="30"/>
+      <c r="M98" s="30"/>
+      <c r="N98" s="30"/>
+      <c r="O98" s="30"/>
+      <c r="P98" s="30"/>
+      <c r="Q98" s="30"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="29"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="29"/>
-      <c r="F99" s="29"/>
-      <c r="G99" s="29"/>
-      <c r="H99" s="29"/>
-      <c r="I99" s="29"/>
-      <c r="J99" s="29"/>
-      <c r="K99" s="29"/>
-      <c r="L99" s="29"/>
-      <c r="M99" s="29"/>
-      <c r="N99" s="29"/>
-      <c r="O99" s="29"/>
-      <c r="P99" s="29"/>
-      <c r="Q99" s="29"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="30"/>
+      <c r="K99" s="30"/>
+      <c r="L99" s="30"/>
+      <c r="M99" s="30"/>
+      <c r="N99" s="30"/>
+      <c r="O99" s="30"/>
+      <c r="P99" s="30"/>
+      <c r="Q99" s="30"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="29"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
-      <c r="D100" s="29"/>
-      <c r="E100" s="29"/>
-      <c r="F100" s="29"/>
-      <c r="G100" s="29"/>
-      <c r="H100" s="29"/>
-      <c r="I100" s="29"/>
-      <c r="J100" s="29"/>
-      <c r="K100" s="29"/>
-      <c r="L100" s="29"/>
-      <c r="M100" s="29"/>
-      <c r="N100" s="29"/>
-      <c r="O100" s="29"/>
-      <c r="P100" s="29"/>
-      <c r="Q100" s="29"/>
+      <c r="A100" s="30"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="30"/>
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
+      <c r="M100" s="30"/>
+      <c r="N100" s="30"/>
+      <c r="O100" s="30"/>
+      <c r="P100" s="30"/>
+      <c r="Q100" s="30"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="29"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
-      <c r="E101" s="29"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="29"/>
-      <c r="H101" s="29"/>
-      <c r="I101" s="29"/>
-      <c r="J101" s="29"/>
-      <c r="K101" s="29"/>
-      <c r="L101" s="29"/>
-      <c r="M101" s="29"/>
-      <c r="N101" s="29"/>
-      <c r="O101" s="29"/>
-      <c r="P101" s="29"/>
-      <c r="Q101" s="29"/>
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="30"/>
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
+      <c r="M101" s="30"/>
+      <c r="N101" s="30"/>
+      <c r="O101" s="30"/>
+      <c r="P101" s="30"/>
+      <c r="Q101" s="30"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="29"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
-      <c r="E102" s="29"/>
-      <c r="F102" s="29"/>
-      <c r="G102" s="29"/>
-      <c r="H102" s="29"/>
-      <c r="I102" s="29"/>
-      <c r="J102" s="29"/>
-      <c r="K102" s="29"/>
-      <c r="L102" s="29"/>
-      <c r="M102" s="29"/>
-      <c r="N102" s="29"/>
-      <c r="O102" s="29"/>
-      <c r="P102" s="29"/>
-      <c r="Q102" s="29"/>
+      <c r="A102" s="30"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+      <c r="H102" s="30"/>
+      <c r="I102" s="30"/>
+      <c r="J102" s="30"/>
+      <c r="K102" s="30"/>
+      <c r="L102" s="30"/>
+      <c r="M102" s="30"/>
+      <c r="N102" s="30"/>
+      <c r="O102" s="30"/>
+      <c r="P102" s="30"/>
+      <c r="Q102" s="30"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="29"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
-      <c r="E103" s="29"/>
-      <c r="F103" s="29"/>
-      <c r="G103" s="29"/>
-      <c r="H103" s="29"/>
-      <c r="I103" s="29"/>
-      <c r="J103" s="29"/>
-      <c r="K103" s="29"/>
-      <c r="L103" s="29"/>
-      <c r="M103" s="29"/>
-      <c r="N103" s="29"/>
-      <c r="O103" s="29"/>
-      <c r="P103" s="29"/>
-      <c r="Q103" s="29"/>
+      <c r="A103" s="30"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
+      <c r="I103" s="30"/>
+      <c r="J103" s="30"/>
+      <c r="K103" s="30"/>
+      <c r="L103" s="30"/>
+      <c r="M103" s="30"/>
+      <c r="N103" s="30"/>
+      <c r="O103" s="30"/>
+      <c r="P103" s="30"/>
+      <c r="Q103" s="30"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="29"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
-      <c r="D104" s="29"/>
-      <c r="E104" s="29"/>
-      <c r="F104" s="29"/>
-      <c r="G104" s="29"/>
-      <c r="H104" s="29"/>
-      <c r="I104" s="29"/>
-      <c r="J104" s="29"/>
-      <c r="K104" s="29"/>
-      <c r="L104" s="29"/>
-      <c r="M104" s="29"/>
-      <c r="N104" s="29"/>
-      <c r="O104" s="29"/>
-      <c r="P104" s="29"/>
-      <c r="Q104" s="29"/>
+      <c r="A104" s="30"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="30"/>
+      <c r="J104" s="30"/>
+      <c r="K104" s="30"/>
+      <c r="L104" s="30"/>
+      <c r="M104" s="30"/>
+      <c r="N104" s="30"/>
+      <c r="O104" s="30"/>
+      <c r="P104" s="30"/>
+      <c r="Q104" s="30"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="29"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="29"/>
-      <c r="F105" s="29"/>
-      <c r="G105" s="29"/>
-      <c r="H105" s="29"/>
-      <c r="I105" s="29"/>
-      <c r="J105" s="29"/>
-      <c r="K105" s="29"/>
-      <c r="L105" s="29"/>
-      <c r="M105" s="29"/>
-      <c r="N105" s="29"/>
-      <c r="O105" s="29"/>
-      <c r="P105" s="29"/>
-      <c r="Q105" s="29"/>
+      <c r="A105" s="30"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="30"/>
+      <c r="J105" s="30"/>
+      <c r="K105" s="30"/>
+      <c r="L105" s="30"/>
+      <c r="M105" s="30"/>
+      <c r="N105" s="30"/>
+      <c r="O105" s="30"/>
+      <c r="P105" s="30"/>
+      <c r="Q105" s="30"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="29"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="29"/>
-      <c r="D106" s="29"/>
-      <c r="E106" s="29"/>
-      <c r="F106" s="29"/>
-      <c r="G106" s="29"/>
-      <c r="H106" s="29"/>
-      <c r="I106" s="29"/>
-      <c r="J106" s="29"/>
-      <c r="K106" s="29"/>
-      <c r="L106" s="29"/>
-      <c r="M106" s="29"/>
-      <c r="N106" s="29"/>
-      <c r="O106" s="29"/>
-      <c r="P106" s="29"/>
-      <c r="Q106" s="29"/>
+      <c r="A106" s="30"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
+      <c r="D106" s="30"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
+      <c r="I106" s="30"/>
+      <c r="J106" s="30"/>
+      <c r="K106" s="30"/>
+      <c r="L106" s="30"/>
+      <c r="M106" s="30"/>
+      <c r="N106" s="30"/>
+      <c r="O106" s="30"/>
+      <c r="P106" s="30"/>
+      <c r="Q106" s="30"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="29"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="29"/>
-      <c r="F107" s="29"/>
-      <c r="G107" s="29"/>
-      <c r="H107" s="29"/>
-      <c r="I107" s="29"/>
-      <c r="J107" s="29"/>
-      <c r="K107" s="29"/>
-      <c r="L107" s="29"/>
-      <c r="M107" s="29"/>
-      <c r="N107" s="29"/>
-      <c r="O107" s="29"/>
-      <c r="P107" s="29"/>
-      <c r="Q107" s="29"/>
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+      <c r="D107" s="30"/>
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+      <c r="H107" s="30"/>
+      <c r="I107" s="30"/>
+      <c r="J107" s="30"/>
+      <c r="K107" s="30"/>
+      <c r="L107" s="30"/>
+      <c r="M107" s="30"/>
+      <c r="N107" s="30"/>
+      <c r="O107" s="30"/>
+      <c r="P107" s="30"/>
+      <c r="Q107" s="30"/>
     </row>
     <row r="108" ht="14.25" customHeight="1"/>
     <row r="109" ht="14.25" customHeight="1"/>
